--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F375"/>
+  <dimension ref="A1:F376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9432,6 +9432,30 @@
         <v>393.59</v>
       </c>
       <c r="F375" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="C376" t="n">
+        <v>375.63</v>
+      </c>
+      <c r="D376" t="n">
+        <v>386.67</v>
+      </c>
+      <c r="E376" t="n">
+        <v>393.88</v>
+      </c>
+      <c r="F376" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9448,7 +9472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B400"/>
+  <dimension ref="A1:B401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13451,6 +13475,16 @@
       </c>
       <c r="B400" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -13619,28 +13653,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06784174758883744</v>
+        <v>0.06287740039921892</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02035541618967229</v>
+        <v>0.01731091455359324</v>
       </c>
       <c r="M2" t="n">
-        <v>2.815263098913077</v>
+        <v>2.833306597113713</v>
       </c>
       <c r="N2" t="n">
-        <v>11.99013767579502</v>
+        <v>12.1870589865135</v>
       </c>
       <c r="O2" t="n">
-        <v>3.462677818653508</v>
+        <v>3.490996847107356</v>
       </c>
       <c r="P2" t="n">
-        <v>367.7291003515339</v>
+        <v>367.7808315253773</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13697,28 +13731,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0597710655241225</v>
+        <v>0.0584248129999693</v>
       </c>
       <c r="J3" t="n">
+        <v>375</v>
+      </c>
+      <c r="K3" t="n">
         <v>374</v>
       </c>
-      <c r="K3" t="n">
-        <v>373</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02007396218135815</v>
+        <v>0.01927320403097121</v>
       </c>
       <c r="M3" t="n">
-        <v>2.547604171677367</v>
+        <v>2.547027854948748</v>
       </c>
       <c r="N3" t="n">
-        <v>9.463798274068285</v>
+        <v>9.455382023865583</v>
       </c>
       <c r="O3" t="n">
-        <v>3.07632870058911</v>
+        <v>3.074960491431651</v>
       </c>
       <c r="P3" t="n">
-        <v>376.5799113007618</v>
+        <v>376.5939270964705</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13775,28 +13809,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07709927545583252</v>
+        <v>0.0770599439015289</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02905081142943389</v>
+        <v>0.02918672812880796</v>
       </c>
       <c r="M4" t="n">
-        <v>2.434106686633209</v>
+        <v>2.427834272474657</v>
       </c>
       <c r="N4" t="n">
-        <v>10.75425649612681</v>
+        <v>10.7255928467354</v>
       </c>
       <c r="O4" t="n">
-        <v>3.279368307483442</v>
+        <v>3.274995091100962</v>
       </c>
       <c r="P4" t="n">
-        <v>384.7122868450738</v>
+        <v>384.712696701072</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13853,28 +13887,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04538388246682789</v>
+        <v>0.04856063823076404</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009170660573355138</v>
+        <v>0.01046537603501474</v>
       </c>
       <c r="M5" t="n">
-        <v>2.636077790704198</v>
+        <v>2.644778702967646</v>
       </c>
       <c r="N5" t="n">
-        <v>12.0460064476519</v>
+        <v>12.10761399459874</v>
       </c>
       <c r="O5" t="n">
-        <v>3.47073572137838</v>
+        <v>3.47959968884335</v>
       </c>
       <c r="P5" t="n">
-        <v>386.7332636065969</v>
+        <v>386.7001600990449</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13912,7 +13946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F375"/>
+  <dimension ref="A1:F376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25911,6 +25945,38 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-35.42906033340949,174.43145233440717</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-35.429774556794115,174.43129448036632</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-35.43046441581595,174.4312321549165</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-35.431133573657085,174.4314229317194</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F376"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9456,6 +9456,54 @@
         <v>393.88</v>
       </c>
       <c r="F376" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="C377" t="n">
+        <v>374.37</v>
+      </c>
+      <c r="D377" t="n">
+        <v>386.03</v>
+      </c>
+      <c r="E377" t="n">
+        <v>393.4</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>364.28</v>
+      </c>
+      <c r="C378" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="D378" t="n">
+        <v>386.05</v>
+      </c>
+      <c r="E378" t="n">
+        <v>392.67</v>
+      </c>
+      <c r="F378" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9472,7 +9520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B401"/>
+  <dimension ref="A1:B403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13485,6 +13533,26 @@
       </c>
       <c r="B401" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -13653,28 +13721,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06287740039921892</v>
+        <v>0.05604066424138397</v>
       </c>
       <c r="J2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01731091455359324</v>
+        <v>0.01370826374179557</v>
       </c>
       <c r="M2" t="n">
-        <v>2.833306597113713</v>
+        <v>2.853398927736683</v>
       </c>
       <c r="N2" t="n">
-        <v>12.1870589865135</v>
+        <v>12.34847402160157</v>
       </c>
       <c r="O2" t="n">
-        <v>3.490996847107356</v>
+        <v>3.514039558912444</v>
       </c>
       <c r="P2" t="n">
-        <v>367.7808315253773</v>
+        <v>367.8524012637154</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13731,28 +13799,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0584248129999693</v>
+        <v>0.0544146421571319</v>
       </c>
       <c r="J3" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K3" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01927320403097121</v>
+        <v>0.01682303279518582</v>
       </c>
       <c r="M3" t="n">
-        <v>2.547027854948748</v>
+        <v>2.551835157229685</v>
       </c>
       <c r="N3" t="n">
-        <v>9.455382023865583</v>
+        <v>9.480021095151546</v>
       </c>
       <c r="O3" t="n">
-        <v>3.074960491431651</v>
+        <v>3.07896428935958</v>
       </c>
       <c r="P3" t="n">
-        <v>376.5939270964705</v>
+        <v>376.6358777572134</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13809,28 +13877,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0770599439015289</v>
+        <v>0.07631184013995876</v>
       </c>
       <c r="J4" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K4" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02918672812880796</v>
+        <v>0.0289592996739354</v>
       </c>
       <c r="M4" t="n">
-        <v>2.427834272474657</v>
+        <v>2.419052563740146</v>
       </c>
       <c r="N4" t="n">
-        <v>10.7255928467354</v>
+        <v>10.67129267853002</v>
       </c>
       <c r="O4" t="n">
-        <v>3.274995091100962</v>
+        <v>3.266694457479919</v>
       </c>
       <c r="P4" t="n">
-        <v>384.712696701072</v>
+        <v>384.7205296090897</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13887,28 +13955,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04856063823076404</v>
+        <v>0.05391289511128652</v>
       </c>
       <c r="J5" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K5" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01046537603501474</v>
+        <v>0.01287638781480027</v>
       </c>
       <c r="M5" t="n">
-        <v>2.644778702967646</v>
+        <v>2.657809234220439</v>
       </c>
       <c r="N5" t="n">
-        <v>12.10761399459874</v>
+        <v>12.17717650295373</v>
       </c>
       <c r="O5" t="n">
-        <v>3.47959968884335</v>
+        <v>3.489581135745912</v>
       </c>
       <c r="P5" t="n">
-        <v>386.7001600990449</v>
+        <v>386.6441236395495</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13946,7 +14014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F376"/>
+  <dimension ref="A1:F378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25977,6 +26045,70 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-35.42906504898527,174.43146770105673</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-35.42977142620557,174.43128113981658</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-35.430464233922905,174.43122510919244</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-35.43113417732136,174.4314176964547</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:12:07+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-35.42907321420574,174.4314943090849</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-35.42977132682177,174.43128071630707</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-35.430464239607076,174.43122532937133</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-35.43113509539365,174.43140973448953</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F378"/>
+  <dimension ref="A1:F380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9506,6 +9506,54 @@
       <c r="F378" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>367.18</v>
+      </c>
+      <c r="C379" t="n">
+        <v>374.07</v>
+      </c>
+      <c r="D379" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="E379" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>366.44</v>
+      </c>
+      <c r="C380" t="n">
+        <v>373.78</v>
+      </c>
+      <c r="D380" t="n">
+        <v>386.24</v>
+      </c>
+      <c r="E380" t="n">
+        <v>391.23</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B403"/>
+  <dimension ref="A1:B405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13553,6 +13601,26 @@
       </c>
       <c r="B403" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -13721,28 +13789,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05604066424138397</v>
+        <v>0.0533765549222711</v>
       </c>
       <c r="J2" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K2" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01370826374179557</v>
+        <v>0.01256176921091445</v>
       </c>
       <c r="M2" t="n">
-        <v>2.853398927736683</v>
+        <v>2.851972936123925</v>
       </c>
       <c r="N2" t="n">
-        <v>12.34847402160157</v>
+        <v>12.31727313700624</v>
       </c>
       <c r="O2" t="n">
-        <v>3.514039558912444</v>
+        <v>3.509597289861935</v>
       </c>
       <c r="P2" t="n">
-        <v>367.8524012637154</v>
+        <v>367.8804319760081</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13799,28 +13867,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0544146421571319</v>
+        <v>0.05004648386747403</v>
       </c>
       <c r="J3" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K3" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01682303279518582</v>
+        <v>0.01429824713251715</v>
       </c>
       <c r="M3" t="n">
-        <v>2.551835157229685</v>
+        <v>2.558259523255046</v>
       </c>
       <c r="N3" t="n">
-        <v>9.480021095151546</v>
+        <v>9.519643652510219</v>
       </c>
       <c r="O3" t="n">
-        <v>3.07896428935958</v>
+        <v>3.08539197712547</v>
       </c>
       <c r="P3" t="n">
-        <v>376.6358777572134</v>
+        <v>376.6817925896744</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13877,28 +13945,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07631184013995876</v>
+        <v>0.07585822036899996</v>
       </c>
       <c r="J4" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K4" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0289592996739354</v>
+        <v>0.02894954485249679</v>
       </c>
       <c r="M4" t="n">
-        <v>2.419052563740146</v>
+        <v>2.408736098552026</v>
       </c>
       <c r="N4" t="n">
-        <v>10.67129267853002</v>
+        <v>10.61597093566241</v>
       </c>
       <c r="O4" t="n">
-        <v>3.266694457479919</v>
+        <v>3.258215912990176</v>
       </c>
       <c r="P4" t="n">
-        <v>384.7205296090897</v>
+        <v>384.7253025150703</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13955,28 +14023,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05391289511128652</v>
+        <v>0.05727319333992703</v>
       </c>
       <c r="J5" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K5" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01287638781480027</v>
+        <v>0.01461243235544285</v>
       </c>
       <c r="M5" t="n">
-        <v>2.657809234220439</v>
+        <v>2.660873981491783</v>
       </c>
       <c r="N5" t="n">
-        <v>12.17717650295373</v>
+        <v>12.16582952676715</v>
       </c>
       <c r="O5" t="n">
-        <v>3.489581135745912</v>
+        <v>3.487954920403523</v>
       </c>
       <c r="P5" t="n">
-        <v>386.6441236395495</v>
+        <v>386.6087732094696</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14014,7 +14082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F378"/>
+  <dimension ref="A1:F380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26109,6 +26177,70 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-35.42908239215953,174.43152421733987</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-35.429770680827104,174.43127796349535</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-35.43046433339571,174.4312289623228</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-35.43113681834987,174.43139479217075</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-35.42908005019962,174.43151658557764</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-35.42976996029452,174.43127489305158</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-35.430464293606605,174.43122742107064</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-35.43113690638408,174.43139402869463</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F380"/>
+  <dimension ref="A1:F383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9554,6 +9554,78 @@
       <c r="F380" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>366.97</v>
+      </c>
+      <c r="C381" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="D381" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="E381" t="n">
+        <v>390.29</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>365.19</v>
+      </c>
+      <c r="C382" t="n">
+        <v>371.56</v>
+      </c>
+      <c r="D382" t="n">
+        <v>384.11</v>
+      </c>
+      <c r="E382" t="n">
+        <v>387.54</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>365.69</v>
+      </c>
+      <c r="C383" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="D383" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="E383" t="n">
+        <v>388.54</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B405"/>
+  <dimension ref="A1:B408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13621,6 +13693,36 @@
       </c>
       <c r="B405" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -13789,28 +13891,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0533765549222711</v>
+        <v>0.0481726208239781</v>
       </c>
       <c r="J2" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K2" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01256176921091445</v>
+        <v>0.01035718569736055</v>
       </c>
       <c r="M2" t="n">
-        <v>2.851972936123925</v>
+        <v>2.855776766015396</v>
       </c>
       <c r="N2" t="n">
-        <v>12.31727313700624</v>
+        <v>12.31093735668826</v>
       </c>
       <c r="O2" t="n">
-        <v>3.509597289861935</v>
+        <v>3.508694537386841</v>
       </c>
       <c r="P2" t="n">
-        <v>367.8804319760081</v>
+        <v>367.9354100250641</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13867,28 +13969,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05004648386747403</v>
+        <v>0.0407378755131258</v>
       </c>
       <c r="J3" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K3" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01429824713251715</v>
+        <v>0.009407382984610413</v>
       </c>
       <c r="M3" t="n">
-        <v>2.558259523255046</v>
+        <v>2.57991220525315</v>
       </c>
       <c r="N3" t="n">
-        <v>9.519643652510219</v>
+        <v>9.725641843953346</v>
       </c>
       <c r="O3" t="n">
-        <v>3.08539197712547</v>
+        <v>3.118596133511575</v>
       </c>
       <c r="P3" t="n">
-        <v>376.6817925896744</v>
+        <v>376.7800490772089</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13945,28 +14047,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07585822036899996</v>
+        <v>0.07254878382728196</v>
       </c>
       <c r="J4" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K4" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02894954485249679</v>
+        <v>0.02690107343357229</v>
       </c>
       <c r="M4" t="n">
-        <v>2.408736098552026</v>
+        <v>2.407495141138169</v>
       </c>
       <c r="N4" t="n">
-        <v>10.61597093566241</v>
+        <v>10.57064568138687</v>
       </c>
       <c r="O4" t="n">
-        <v>3.258215912990176</v>
+        <v>3.251252940235021</v>
       </c>
       <c r="P4" t="n">
-        <v>384.7253025150703</v>
+        <v>384.7602697228066</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14023,28 +14125,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05727319333992703</v>
+        <v>0.05829009817509211</v>
       </c>
       <c r="J5" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K5" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01461243235544285</v>
+        <v>0.01537143356491888</v>
       </c>
       <c r="M5" t="n">
-        <v>2.660873981491783</v>
+        <v>2.648274951522354</v>
       </c>
       <c r="N5" t="n">
-        <v>12.16582952676715</v>
+        <v>12.08374333523603</v>
       </c>
       <c r="O5" t="n">
-        <v>3.487954920403523</v>
+        <v>3.476167909528542</v>
       </c>
       <c r="P5" t="n">
-        <v>386.6087732094696</v>
+        <v>386.5980419259344</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14082,7 +14184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F380"/>
+  <dimension ref="A1:F383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26241,6 +26343,102 @@
         </is>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-35.42908172754934,174.43152205156946</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-35.429768345307416,174.43126801102258</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-35.430464088976585,174.43121949463108</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-35.43113808855728,174.4313837763003</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-35.429076094185156,174.43150369408835</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-35.42976444449075,174.43125138827668</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-35.43046368824129,174.43120397202034</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-35.43114154703777,174.43135378259157</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-35.42907767659111,174.43150885068394</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-35.429763972417234,174.43124937660687</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-35.43046371382019,174.4312049628253</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-35.431140289409356,174.43136468939505</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F383"/>
+  <dimension ref="A1:F386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9624,6 +9624,78 @@
         <v>388.54</v>
       </c>
       <c r="F383" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:57+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>366.57</v>
+      </c>
+      <c r="C384" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="D384" t="n">
+        <v>384.68</v>
+      </c>
+      <c r="E384" t="n">
+        <v>390.05</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="C385" t="n">
+        <v>371.65</v>
+      </c>
+      <c r="D385" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="E385" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>365.79</v>
+      </c>
+      <c r="C386" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="D386" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="E386" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="F386" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9640,7 +9712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B408"/>
+  <dimension ref="A1:B411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13723,6 +13795,36 @@
       </c>
       <c r="B408" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -13891,28 +13993,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0481726208239781</v>
+        <v>0.04366533588973688</v>
       </c>
       <c r="J2" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01035718569736055</v>
+        <v>0.008623878283321118</v>
       </c>
       <c r="M2" t="n">
-        <v>2.855776766015396</v>
+        <v>2.855953814779456</v>
       </c>
       <c r="N2" t="n">
-        <v>12.31093735668826</v>
+        <v>12.2820983915587</v>
       </c>
       <c r="O2" t="n">
-        <v>3.508694537386841</v>
+        <v>3.504582484627619</v>
       </c>
       <c r="P2" t="n">
-        <v>367.9354100250641</v>
+        <v>367.9832223380764</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13969,28 +14071,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0407378755131258</v>
+        <v>0.03202646114557704</v>
       </c>
       <c r="J3" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009407382984610413</v>
+        <v>0.005784918621540625</v>
       </c>
       <c r="M3" t="n">
-        <v>2.57991220525315</v>
+        <v>2.599560607646884</v>
       </c>
       <c r="N3" t="n">
-        <v>9.725641843953346</v>
+        <v>9.901262202674816</v>
       </c>
       <c r="O3" t="n">
-        <v>3.118596133511575</v>
+        <v>3.146627115289452</v>
       </c>
       <c r="P3" t="n">
-        <v>376.7800490772089</v>
+        <v>376.872359755466</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14047,28 +14149,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07254878382728196</v>
+        <v>0.06893070100798537</v>
       </c>
       <c r="J4" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02690107343357229</v>
+        <v>0.0246573566929037</v>
       </c>
       <c r="M4" t="n">
-        <v>2.407495141138169</v>
+        <v>2.408261664037978</v>
       </c>
       <c r="N4" t="n">
-        <v>10.57064568138687</v>
+        <v>10.53171773564664</v>
       </c>
       <c r="O4" t="n">
-        <v>3.251252940235021</v>
+        <v>3.245260811652377</v>
       </c>
       <c r="P4" t="n">
-        <v>384.7602697228066</v>
+        <v>384.7986509455918</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14125,28 +14227,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05829009817509211</v>
+        <v>0.05890834639146179</v>
       </c>
       <c r="J5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01537143356491888</v>
+        <v>0.01594574758978762</v>
       </c>
       <c r="M5" t="n">
-        <v>2.648274951522354</v>
+        <v>2.634588966815421</v>
       </c>
       <c r="N5" t="n">
-        <v>12.08374333523603</v>
+        <v>12.00026803970369</v>
       </c>
       <c r="O5" t="n">
-        <v>3.476167909528542</v>
+        <v>3.464140303120485</v>
       </c>
       <c r="P5" t="n">
-        <v>386.5980419259344</v>
+        <v>386.5915057514315</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14184,7 +14286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F383"/>
+  <dimension ref="A1:F386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26439,6 +26541,102 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:57+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-35.42908046162504,174.4315179262926</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-35.42976484202631,174.43125308231438</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-35.430463850240905,174.4312102471183</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-35.43113839038861,174.43138115866762</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-35.42908008184773,174.43151668870956</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-35.42976466810451,174.4312523411729</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-35.43046377066218,174.43120716461405</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-35.43114070442684,174.43136109014995</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-35.429077993072276,174.43150988200307</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-35.429768295615496,174.43126779926783</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-35.430463628557135,174.43120166014214</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-35.43114168537683,174.43135258284318</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F386"/>
+  <dimension ref="A1:F388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9696,6 +9696,54 @@
         <v>387.43</v>
       </c>
       <c r="F386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="C387" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="D387" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="E387" t="n">
+        <v>388.15</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>364.46</v>
+      </c>
+      <c r="C388" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="D388" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="E388" t="n">
+        <v>388.24</v>
+      </c>
+      <c r="F388" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9712,7 +9760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B411"/>
+  <dimension ref="A1:B413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13825,6 +13873,26 @@
       </c>
       <c r="B411" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -13993,28 +14061,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04366533588973688</v>
+        <v>0.03928250091464607</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K2" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008623878283321118</v>
+        <v>0.007014980965515893</v>
       </c>
       <c r="M2" t="n">
-        <v>2.855953814779456</v>
+        <v>2.862682963592673</v>
       </c>
       <c r="N2" t="n">
-        <v>12.2820983915587</v>
+        <v>12.31475646447359</v>
       </c>
       <c r="O2" t="n">
-        <v>3.504582484627619</v>
+        <v>3.509238730048668</v>
       </c>
       <c r="P2" t="n">
-        <v>367.9832223380764</v>
+        <v>368.0299242859965</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14071,28 +14139,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03202646114557704</v>
+        <v>0.02849554002364505</v>
       </c>
       <c r="J3" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005784918621540625</v>
+        <v>0.004607927717996341</v>
       </c>
       <c r="M3" t="n">
-        <v>2.599560607646884</v>
+        <v>2.6025553010054</v>
       </c>
       <c r="N3" t="n">
-        <v>9.901262202674816</v>
+        <v>9.912202989423971</v>
       </c>
       <c r="O3" t="n">
-        <v>3.146627115289452</v>
+        <v>3.14836512962267</v>
       </c>
       <c r="P3" t="n">
-        <v>376.872359755466</v>
+        <v>376.9099509708942</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14149,28 +14217,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06893070100798537</v>
+        <v>0.06748449578318577</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K4" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0246573566929037</v>
+        <v>0.02389619155932832</v>
       </c>
       <c r="M4" t="n">
-        <v>2.408261664037978</v>
+        <v>2.403528356095898</v>
       </c>
       <c r="N4" t="n">
-        <v>10.53171773564664</v>
+        <v>10.48785563212204</v>
       </c>
       <c r="O4" t="n">
-        <v>3.245260811652377</v>
+        <v>3.238495890397584</v>
       </c>
       <c r="P4" t="n">
-        <v>384.7986509455918</v>
+        <v>384.8140596666208</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14227,28 +14295,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05890834639146179</v>
+        <v>0.0589318114614227</v>
       </c>
       <c r="J5" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01594574758978762</v>
+        <v>0.01613632785665697</v>
       </c>
       <c r="M5" t="n">
-        <v>2.634588966815421</v>
+        <v>2.62119825156036</v>
       </c>
       <c r="N5" t="n">
-        <v>12.00026803970369</v>
+        <v>11.93826368280471</v>
       </c>
       <c r="O5" t="n">
-        <v>3.464140303120485</v>
+        <v>3.455179254800641</v>
       </c>
       <c r="P5" t="n">
-        <v>386.5915057514315</v>
+        <v>386.5912555023473</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14286,7 +14354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F386"/>
+  <dimension ref="A1:F388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26637,6 +26705,70 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>-35.429076062537035,174.43150359095645</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>-35.42977080505685,174.43127849288223</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-35.4304639497142,174.4312141002486</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-35.43114077988455,174.43136043574174</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>-35.429073783872056,174.43149616545918</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>-35.42977140135961,174.4312810339392</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-35.430464054871535,174.43121817355782</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-35.43114066669798,174.43136141735405</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
